--- a/docs/fem/files/xslope_piles_fem_nopile.xlsx
+++ b/docs/fem/files/xslope_piles_fem_nopile.xlsx
@@ -5565,7 +5565,9 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>2000000</v>
       </c>
